--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,59 +905,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133697813</v>
+        <v>136707264</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO Skäktetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325824</v>
+        <v>325772</v>
       </c>
       <c r="R4" t="n">
         <v>6557161</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,23 +984,136 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707264</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133697813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO Skäktetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>325824</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557161</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133697813</t>
         </is>
@@ -1022,6 +1124,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136707264</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136707264</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133697884</v>
+        <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>81355</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Skäktetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325827</v>
+        <v>325856</v>
       </c>
       <c r="R2" t="n">
-        <v>6557077</v>
+        <v>6556999</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +759,48 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697884</t>
+          <t>https://artportalen.se/Sighting/136890122</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133697709</v>
+        <v>133697884</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>81355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,33 +808,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325728</v>
+        <v>325827</v>
       </c>
       <c r="R3" t="n">
-        <v>6557156</v>
+        <v>6557077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +873,6 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,16 +897,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697709</t>
+          <t>https://artportalen.se/Sighting/133697884</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136707264</v>
+        <v>133697709</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,20 +931,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>NO Skäktetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325772</v>
+        <v>325728</v>
       </c>
       <c r="R4" t="n">
-        <v>6557161</v>
+        <v>6557156</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +979,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,82 +998,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707264</t>
+          <t>https://artportalen.se/Sighting/133697709</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133697813</v>
+        <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO Skäktetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325824</v>
+        <v>325772</v>
       </c>
       <c r="R5" t="n">
         <v>6557161</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,12 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,25 +1101,1935 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136707264</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136890116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>325749</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6557176</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890116</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136890129</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>325827</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6557080</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890129</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136890130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>325825</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557097</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890130</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136890131</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325806</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557123</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890131</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136890132</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325817</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6557123</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890132</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136890133</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>325819</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557156</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890133</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136890251</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325732</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6557141</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890251</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136890123</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325858</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557002</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136890118</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>325755</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557123</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890118</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136890121</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325779</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557076</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890121</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136890124</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325904</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557028</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890124</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136890126</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>325889</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557054</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890126</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136890127</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325872</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557080</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890127</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133697813</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO Skäktetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325824</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557161</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133697813</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136890128</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325844</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557070</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890128</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136890117</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>325753</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6557133</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890117</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136890120</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>325762</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6557109</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890120</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136890125</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>325888</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6557033</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890125</t>
         </is>
       </c>
     </row>
@@ -1125,6 +3039,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92097</v>
+        <v>92099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92099</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92102</v>
+        <v>92108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92108</v>
+        <v>92112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92114</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>136890120</v>
       </c>
       <c r="B22" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>136890120</v>
       </c>
       <c r="B22" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -2710,11 +2710,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -2834,11 +2830,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2942,11 +2934,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92129</v>
+        <v>92132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136707264</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92132</v>
+        <v>92142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136890117</v>
       </c>
       <c r="B21" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136890120</v>
       </c>
       <c r="B22" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>136890125</v>
       </c>
       <c r="B23" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92142</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>136890128</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>136890120</v>
       </c>
       <c r="B22" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22939-2026 artfynd.xlsx
+++ b/artfynd/A 22939-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136890122</v>
       </c>
       <c r="B2" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136890116</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136890129</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136890130</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136890131</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136890132</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136890133</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>136890251</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136890123</v>
       </c>
       <c r="B13" t="n">
-        <v>92146</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890118</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890121</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890124</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890126</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890127</v>
       </c>
       <c r="B18" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
